--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-diagnosticreport-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-diagnosticreport-dentaloral-ecs.xlsx
@@ -490,8 +490,7 @@
 </t>
   </si>
   <si>
-    <t>レポートを識別するビジネス識別子  
-【JP Core仕様】当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。</t>
+    <t>レポートを識別するビジネス識別子 【JP Core仕様】当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。</t>
   </si>
   <si>
     <t>例：電子カルテ等のオーダ番号、レポート番号、実施日に連番を付加した番号など</t>
@@ -523,8 +522,7 @@
 </t>
   </si>
   <si>
-    <t>元になった検査や診断の依頼  
-【JP Core仕様】オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
+    <t>元になった検査や診断の依頼  【JP Core仕様】オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
   </si>
   <si>
     <t>通常、１結果ごとに１つの検査依頼があるが、状況によっては、複数の検査要求に対して１レポートがある場合がある。また１つの検査依頼に対して複数のレポートが作成される場合もあることに注意。</t>
@@ -545,8 +543,7 @@
     <t>DiagnosticReport.status</t>
   </si>
   <si>
-    <t>診断レポートのステータス  
-【JP Core仕様】レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
+    <t>診断レポートのステータス  【JP Core仕様】レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
   </si>
   <si>
     <t>診断サービスは、暫定/不完全なレポートを日常的に発行し、以前にリリースされたレポートを撤回することもあります。 / Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
@@ -817,8 +814,7 @@
 </t>
   </si>
   <si>
-    <t>この診断レポートの名前/コード
-【JP Core仕様】診断レポート種別「診療情報提供書」を表す文書コード 57133-1 を指定</t>
+    <t>この診断レポートの名前/コード 【JP Core仕様】診断レポート種別「診療情報提供書」を表す文書コード 57133-1 を指定</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -856,8 +852,7 @@
 </t>
   </si>
   <si>
-    <t>レポートの対象、常にではないが、通常は患者
-【JP Core仕様】Patientリソースを参照</t>
+    <t>レポートの対象、常にではないが、通常は患者 【JP Core仕様】Patientリソースを参照</t>
   </si>
   <si>
     <t>レポートの対象、通常、Patientリソースへの参照。ただし、他のさまざまなソースから収集された検体を対象とすることもある。参照は内容に辿り着ける（解決できる）必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。</t>
@@ -889,8 +884,7 @@
 </t>
   </si>
   <si>
-    <t>依頼時におけるヘルスケアイベント（受診など）
-【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
+    <t>依頼時におけるヘルスケアイベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
   </si>
   <si>
     <t>例：診療、歯科健診（検診） ※JP Coreに網羅されていない</t>
@@ -922,8 +916,7 @@
 </t>
   </si>
   <si>
-    <t>臨床的に関連する時刻または時間  
-【JP Core仕様】レポート作成日時</t>
+    <t>臨床的に関連する時刻または時間  【JP Core仕様】レポート作成日時</t>
   </si>
   <si>
     <t>観測値が関連する時間または期間。レポートの対象が患者である場合、これは通常、読影開始の時間であり、日付／時刻自体のみ提供される。実施日時。</t>
@@ -955,8 +948,7 @@
 </t>
   </si>
   <si>
-    <t>このバージョンが作成された日時  
-【JP Core仕様】最新のレポート確定日時</t>
+    <t>このバージョンが作成された日時  【JP Core仕様】最新のレポート確定日時</t>
   </si>
   <si>
     <t>通常、レポートがレビューおよび検証・確定された後となる。リソース自体の更新時刻とは異なる場合がある。これは、レポートの実際の提供時刻ではなく、リソース自体の更新時刻はレコード（場合によってはセカンダリコピー）のステータスの更新時刻となるため。</t>
@@ -985,8 +977,7 @@
 </t>
   </si>
   <si>
-    <t>レポート内容に責任をもつ診断的サービス  
-【JP Core仕様】レポート確定者</t>
+    <t>レポート内容に責任をもつ診断的サービス 【JP Core仕様】レポート確定者</t>
   </si>
   <si>
     <t>例：歯科医師など</t>
@@ -1014,8 +1005,7 @@
 Reported by</t>
   </si>
   <si>
-    <t>結果の一次解釈者  
-【JP Core仕様】レポートの作成者</t>
+    <t>結果の一次解釈者  【JP Core仕様】レポートの作成者</t>
   </si>
   <si>
     <t>例：歯科医師、歯科研修医など</t>
@@ -1031,8 +1021,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートのもとになった検体に関する情報  
-【JP Core仕様】未使用</t>
+    <t>診断レポートのもとになった検体に関する情報  【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>検査結果名称のコードを見れば検体情報が十分に判明するような場合には、この検体情報は冗長になる。複数の検体が関与する場合には、検査や検査グループごとに検体情報が記述されることがある。</t>
@@ -1055,8 +1044,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートの一部となるObservationsに関する情報  
-【JP Core仕様】検査結果</t>
+    <t>診断レポートの一部となるObservationsに関する情報 【JP Core仕様】検査結果</t>
   </si>
   <si>
     <t>Observationsは階層構造を持てる。</t>
@@ -1098,8 +1086,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートに関連づけられたメディアに関する情報  
-【JP Core仕様】このレポートに関連づけられたキー画像</t>
+    <t>診断レポートに関連づけられたメディアに関する情報 【JP Core仕様】このレポートに関連づけられたキー画像</t>
   </si>
   <si>
     <t>通常は画像。診断プロセス中に作成され、患者から直接取得されたもの、あるいは調製された検体標本（つまり、関心のあるスライド）のこともある。</t>
@@ -1179,8 +1166,7 @@
 </t>
   </si>
   <si>
-    <t>簡潔かつ臨床的な文脈で表現した診断レポートの要約結論（解釈、インプレッション）  
-【JP Core仕様】原則、未使用。レセプト傷病名などテキスト型で記載も可能。</t>
+    <t>簡潔かつ臨床的な文脈で表現した診断レポートの要約結論（解釈、インプレッション） 【JP Core仕様】原則、未使用。レセプト傷病名などテキスト型で記載も可能。</t>
   </si>
   <si>
     <t>基本的な結果データの中で失われない結論を提供できる必要があります。 / Need to be able to provide a conclusion that is not lost among the basic result data.</t>
@@ -1195,8 +1181,7 @@
     <t>DiagnosticReport.conclusionCode</t>
   </si>
   <si>
-    <t>診断レポートの要約結論（解釈、インプレッション）を表すコード  
-【JP Core仕様】原則、未使用。レセプト傷病名などのCodeableConcept型で定義も可能。</t>
+    <t>診断レポートの要約結論（解釈、インプレッション）を表すコード  【JP Core仕様】原則、未使用。レセプト傷病名などのCodeableConcept型で定義も可能。</t>
   </si>
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、独自の構造を提供する必要がある。</t>
